--- a/datasets/circuit_metadata.xlsx
+++ b/datasets/circuit_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VANSH\Formula1\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1994D8-6C84-4301-AAAF-3130ECBC5C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3FDC93-81F3-48A0-84B2-0D6D2F54D847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3288" yWindow="1692" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>GP</t>
   </si>
@@ -100,12 +100,30 @@
   </si>
   <si>
     <t>Abu Dhabi Grand Prix</t>
+  </si>
+  <si>
+    <t>Emilia Romagna Grand Prix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chinese Grand Prix </t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Street</t>
+  </si>
+  <si>
+    <t>SemiPermanent</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -135,8 +153,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,11 +436,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.44140625" customWidth="1"/>
-    <col min="2" max="3" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -439,110 +459,264 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>5.4119999999999999</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3">
+        <v>6.1740000000000004</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>5.2779999999999996</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>6.0030000000000001</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6">
+        <v>5.4119999999999999</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>3.3370000000000002</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>4.657</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>4.3609999999999998</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10">
+        <v>4.3259999999999996</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11">
+        <v>5.891</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12">
+        <v>4.3810000000000002</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13">
+        <v>7.0039999999999996</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14">
+        <v>4.2590000000000003</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15">
+        <v>5.7930000000000001</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1">
+        <v>4.9400000000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17">
+        <v>5.8070000000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18">
+        <v>5.4189999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19">
+        <v>5.5129999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20">
+        <v>4.3040000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21">
+        <v>4.3090000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22">
+        <v>6.2009999999999996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23">
+        <v>5.5129999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24">
+        <v>4.9089999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25">
+        <v>5.4509999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/circuit_metadata.xlsx
+++ b/datasets/circuit_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VANSH\Formula1\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3FDC93-81F3-48A0-84B2-0D6D2F54D847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00075981-7585-4AF7-A23D-D1F083C327C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3288" yWindow="1692" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="36">
   <si>
     <t>GP</t>
   </si>
@@ -105,9 +105,6 @@
     <t>Emilia Romagna Grand Prix</t>
   </si>
   <si>
-    <t xml:space="preserve">Chinese Grand Prix </t>
-  </si>
-  <si>
     <t>Permanent</t>
   </si>
   <si>
@@ -115,6 +112,27 @@
   </si>
   <si>
     <t>SemiPermanent</t>
+  </si>
+  <si>
+    <t>TrackAbrasiveness</t>
+  </si>
+  <si>
+    <t>VeryHigh</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>VeryLow</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Chinese Grand Prix</t>
   </si>
 </sst>
 </file>
@@ -122,7 +140,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -155,7 +173,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,15 +454,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.44140625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -454,269 +473,344 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>5.4119999999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>6.1740000000000004</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>5.2779999999999996</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>6.0030000000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>5.4119999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>3.3370000000000002</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>4.657</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>4.3609999999999998</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10">
         <v>4.3259999999999996</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>5.891</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>4.3810000000000002</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13">
         <v>7.0039999999999996</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <v>4.2590000000000003</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15">
         <v>5.7930000000000001</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1">
         <v>4.9400000000000004</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17">
         <v>5.8070000000000004</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>5.4189999999999996</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19">
         <v>5.5129999999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20">
         <v>4.3040000000000003</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21">
         <v>4.3090000000000002</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22">
         <v>6.2009999999999996</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23">
         <v>5.5129999999999999</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>4.9089999999999998</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25">
         <v>5.4509999999999996</v>
+      </c>
+      <c r="D25" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
